--- a/1_SoftWare/stm32计算器.xlsx
+++ b/1_SoftWare/stm32计算器.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Program\Eshift_CZ\SoftWare\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Program\Eshift_CZ\1_SoftWare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8A72A5-B514-4020-9DB2-BB2F24ED6DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D72241-84B9-4331-9896-F1FD8A527DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>原始时钟</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -85,6 +85,51 @@
   </si>
   <si>
     <t>720</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 Parameter Settings 页配置预分频系数为 71，计数周期(自动加载值)为 499，定时器溢出频率，即PWM的周期，就是 72MHz/(71+1)/(499+1) = 2kHz</t>
+  </si>
+  <si>
+    <t>PWM频率：</t>
+  </si>
+  <si>
+    <t>Fpwm =Tclk / ((arr+1)*(psc+1))(单位：Hz)</t>
+  </si>
+  <si>
+    <t>arr 是计数器值</t>
+  </si>
+  <si>
+    <t>psc 是预分频值</t>
+  </si>
+  <si>
+    <t>占空比：</t>
+  </si>
+  <si>
+    <t>duty circle = TIM3-&gt;CCR1 / arr(单位：%)</t>
+  </si>
+  <si>
+    <t>arr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>72</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KHZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>real</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -92,7 +137,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +161,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -131,19 +186,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -548,74 +608,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.9296875" customWidth="1"/>
+    <col min="1" max="1" width="9.125" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.875" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="7" max="7" width="13.796875" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="86.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="86.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -632,7 +692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>72</v>
       </c>
@@ -651,7 +711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>72</v>
       </c>
@@ -670,7 +730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>72</v>
       </c>
@@ -689,7 +749,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>72</v>
       </c>
@@ -708,7 +768,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>72</v>
       </c>
@@ -727,7 +787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>72</v>
       </c>
@@ -746,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>72</v>
       </c>
@@ -765,7 +825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>168</v>
       </c>
@@ -784,7 +844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>72</v>
       </c>
@@ -802,6 +862,464 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>72</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="3">
+        <f xml:space="preserve"> A36*1000000/(B36*C36)</f>
+        <v>2000</v>
+      </c>
+      <c r="E36" s="2">
+        <f>D36/1000</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>72</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" ref="D37:D44" si="6" xml:space="preserve"> A37*1000000/(B37*C37)</f>
+        <v>1000</v>
+      </c>
+      <c r="E37" s="2">
+        <f>D37/1000</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>72</v>
+      </c>
+      <c r="B38">
+        <v>72</v>
+      </c>
+      <c r="C38">
+        <v>800</v>
+      </c>
+      <c r="D38" s="3">
+        <f t="shared" si="6"/>
+        <v>1250</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" ref="E38:E44" si="7">D38/1000</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>72</v>
+      </c>
+      <c r="B39">
+        <v>72</v>
+      </c>
+      <c r="C39">
+        <v>500</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="6"/>
+        <v>2000</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>72</v>
+      </c>
+      <c r="B40">
+        <v>7200</v>
+      </c>
+      <c r="C40">
+        <v>200</v>
+      </c>
+      <c r="D40" s="3">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>72</v>
+      </c>
+      <c r="B41">
+        <v>720</v>
+      </c>
+      <c r="C41">
+        <v>200</v>
+      </c>
+      <c r="D41" s="3">
+        <f t="shared" si="6"/>
+        <v>500</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>72</v>
+      </c>
+      <c r="B42">
+        <v>7200</v>
+      </c>
+      <c r="C42">
+        <v>50</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="E42" s="2">
+        <f t="shared" si="7"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>168</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>10000</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="6"/>
+        <v>16800</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="7"/>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>84</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>65536</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="6"/>
+        <v>1281.73828125</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="7"/>
+        <v>1.28173828125</v>
+      </c>
+      <c r="G44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>84</v>
+      </c>
+      <c r="B45">
+        <v>84</v>
+      </c>
+      <c r="C45">
+        <v>10000</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" ref="D45:D48" si="8" xml:space="preserve"> A45*1000000/(B45*C45)</f>
+        <v>100</v>
+      </c>
+      <c r="E45" s="2">
+        <f t="shared" ref="E45:E48" si="9">D45/1000</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>84</v>
+      </c>
+      <c r="B46">
+        <v>42</v>
+      </c>
+      <c r="C46">
+        <v>10000</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="E46" s="2">
+        <f t="shared" si="9"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>84</v>
+      </c>
+      <c r="B47">
+        <v>21</v>
+      </c>
+      <c r="C47">
+        <v>10000</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="8"/>
+        <v>400</v>
+      </c>
+      <c r="E47" s="2">
+        <f t="shared" si="9"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>84</v>
+      </c>
+      <c r="B48">
+        <v>10</v>
+      </c>
+      <c r="C48">
+        <v>10000</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="8"/>
+        <v>840</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="9"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>84</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>10000</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" ref="D49:D52" si="10" xml:space="preserve"> A49*1000000/(B49*C49)</f>
+        <v>8400</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" ref="E49:E52" si="11">D49/1000</f>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>84</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>10000</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="10"/>
+        <v>4200</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="11"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>84</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>10000</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="10"/>
+        <v>8400</v>
+      </c>
+      <c r="E51" s="2">
+        <f t="shared" si="11"/>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>84</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>5000</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="10"/>
+        <v>16800</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="11"/>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>84</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>8400</v>
+      </c>
+      <c r="D53" s="3">
+        <f t="shared" ref="D53" si="12" xml:space="preserve"> A53*1000000/(B53*C53)</f>
+        <v>10000</v>
+      </c>
+      <c r="E53" s="2">
+        <f t="shared" ref="E53" si="13">D53/1000</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>84</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>100</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" ref="D54:D57" si="14" xml:space="preserve"> A54*1000000/(B54*C54)</f>
+        <v>840000</v>
+      </c>
+      <c r="E54" s="2">
+        <f t="shared" ref="E54:E57" si="15">D54/1000</f>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>84</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" si="14"/>
+        <v>8400000</v>
+      </c>
+      <c r="E55" s="2">
+        <f t="shared" si="15"/>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>84</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="14"/>
+        <v>84000000</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="15"/>
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D57" s="3"/>
+      <c r="E57" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/1_SoftWare/stm32计算器.xlsx
+++ b/1_SoftWare/stm32计算器.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Program\Eshift_CZ\1_SoftWare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D72241-84B9-4331-9896-F1FD8A527DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F0B1DF-905C-42D5-A4C0-C9E7CB881FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1073" yWindow="1073" windowWidth="17280" windowHeight="9982" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -609,24 +609,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.125" customWidth="1"/>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
+    <col min="1" max="1" width="9.1328125" customWidth="1"/>
+    <col min="2" max="2" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.86328125" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="13.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="86.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="86.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -637,7 +637,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -648,7 +648,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -659,7 +659,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -670,12 +670,12 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -692,7 +692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>72</v>
       </c>
@@ -711,7 +711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>72</v>
       </c>
@@ -730,7 +730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>72</v>
       </c>
@@ -749,7 +749,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>72</v>
       </c>
@@ -768,7 +768,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>72</v>
       </c>
@@ -787,7 +787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>72</v>
       </c>
@@ -806,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>72</v>
       </c>
@@ -825,7 +825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>168</v>
       </c>
@@ -844,61 +844,61 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="B20">
-        <v>7200</v>
+        <v>16800</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="4"/>
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -915,7 +915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>72</v>
       </c>
@@ -934,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>72</v>
       </c>
@@ -953,7 +953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>72</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>72</v>
       </c>
@@ -991,7 +991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>72</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>72</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>72</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>168</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>84</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>84</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>84</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>84</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>84</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>84</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>84</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>84</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>84</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>84</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>84</v>
       </c>
@@ -1271,15 +1271,15 @@
         <v>100</v>
       </c>
       <c r="D54" s="3">
-        <f t="shared" ref="D54:D57" si="14" xml:space="preserve"> A54*1000000/(B54*C54)</f>
+        <f t="shared" ref="D54:D56" si="14" xml:space="preserve"> A54*1000000/(B54*C54)</f>
         <v>840000</v>
       </c>
       <c r="E54" s="2">
-        <f t="shared" ref="E54:E57" si="15">D54/1000</f>
+        <f t="shared" ref="E54:E56" si="15">D54/1000</f>
         <v>840</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>84</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>8400</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>84</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>84000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="D57" s="3"/>
       <c r="E57" s="2"/>
     </row>
